--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N77_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N77_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.61540137421774</v>
+        <v>3.187502723310383</v>
       </c>
       <c r="D2" t="n">
-        <v>46.24719158135765</v>
+        <v>7.515168631970619</v>
       </c>
       <c r="E2" t="n">
-        <v>14.27467954825861</v>
+        <v>2.319635426592025</v>
       </c>
       <c r="F2" t="n">
-        <v>14.14137274346659</v>
+        <v>2.297973070813321</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.533092092075905</v>
+        <v>1.061627464962335</v>
       </c>
       <c r="D3" t="n">
-        <v>32.02112076978237</v>
+        <v>5.203432125089636</v>
       </c>
       <c r="E3" t="n">
-        <v>14.27467954825861</v>
+        <v>2.319635426592025</v>
       </c>
       <c r="F3" t="n">
-        <v>14.14137274346659</v>
+        <v>2.297973070813321</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.47137757058005</v>
+        <v>3.489098855219257</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>2.7625</v>
       </c>
       <c r="E4" t="n">
-        <v>14.27467954825861</v>
+        <v>2.319635426592025</v>
       </c>
       <c r="F4" t="n">
-        <v>14.14137274346659</v>
+        <v>2.297973070813321</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.03573985613188</v>
+        <v>2.930807726621431</v>
       </c>
       <c r="D5" t="n">
-        <v>17.80279363979876</v>
+        <v>2.892953966467299</v>
       </c>
       <c r="E5" t="n">
-        <v>14.27467954825861</v>
+        <v>2.319635426592025</v>
       </c>
       <c r="F5" t="n">
-        <v>14.14137274346659</v>
+        <v>2.297973070813321</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.336512715982316</v>
+        <v>1.192183316347126</v>
       </c>
       <c r="D6" t="n">
-        <v>6.860986365152479</v>
+        <v>1.114910284337278</v>
       </c>
       <c r="E6" t="n">
-        <v>14.27467954825861</v>
+        <v>2.319635426592025</v>
       </c>
       <c r="F6" t="n">
-        <v>14.14137274346659</v>
+        <v>2.297973070813321</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>49.15907196240201</v>
+        <v>7.988349193890327</v>
       </c>
       <c r="D7" t="n">
-        <v>48.67101710876147</v>
+        <v>7.909040280173739</v>
       </c>
       <c r="E7" t="n">
-        <v>14.27467954825861</v>
+        <v>2.319635426592025</v>
       </c>
       <c r="F7" t="n">
-        <v>14.14137274346659</v>
+        <v>2.297973070813321</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.76388437594086</v>
+        <v>4.99913121109039</v>
       </c>
       <c r="D8" t="n">
-        <v>30.90089215621262</v>
+        <v>5.021394975384551</v>
       </c>
       <c r="E8" t="n">
-        <v>14.27467954825861</v>
+        <v>2.319635426592025</v>
       </c>
       <c r="F8" t="n">
-        <v>14.14137274346659</v>
+        <v>2.297973070813321</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>41.55591892553749</v>
+        <v>6.752836825399842</v>
       </c>
       <c r="D9" t="n">
-        <v>41.36935723919613</v>
+        <v>6.722520551369371</v>
       </c>
       <c r="E9" t="n">
-        <v>14.27467954825861</v>
+        <v>2.319635426592025</v>
       </c>
       <c r="F9" t="n">
-        <v>14.14137274346659</v>
+        <v>2.297973070813321</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
